--- a/data_indexpoints_tidy/tallmateriale_20952.xlsx
+++ b/data_indexpoints_tidy/tallmateriale_20952.xlsx
@@ -9,16 +9,17 @@
   <sheets>
     <sheet name="punkt_adt" sheetId="1" r:id="rId1"/>
     <sheet name="punktindeks_maned" sheetId="2" r:id="rId2"/>
-    <sheet name="byindeks_aarlig" sheetId="3" r:id="rId3"/>
-    <sheet name="byindeks_hittil" sheetId="4" r:id="rId4"/>
-    <sheet name="by_glid_indeks" sheetId="5" r:id="rId5"/>
+    <sheet name="punktindeks_aar" sheetId="3" r:id="rId3"/>
+    <sheet name="byindeks_aarlig" sheetId="4" r:id="rId4"/>
+    <sheet name="byindeks_hittil" sheetId="5" r:id="rId5"/>
+    <sheet name="by_glid_indeks" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="189">
   <si>
     <t>trp_id</t>
   </si>
@@ -470,6 +471,12 @@
     <t>des</t>
   </si>
   <si>
+    <t>index_2024_2025</t>
+  </si>
+  <si>
+    <t>index_2025_2026</t>
+  </si>
+  <si>
     <t>area_name</t>
   </si>
   <si>
@@ -521,7 +528,7 @@
     <t>2025-2026</t>
   </si>
   <si>
-    <t>jan-jul</t>
+    <t>jan-aug</t>
   </si>
   <si>
     <t>2024-2026</t>
@@ -576,6 +583,9 @@
   </si>
   <si>
     <t>2024 - (aug 2025 - jul 2026)</t>
+  </si>
+  <si>
+    <t>2024 - (sep 2025 - aug 2026)</t>
   </si>
 </sst>
 </file>
@@ -1339,13 +1349,13 @@
         <v>1740</v>
       </c>
       <c r="M9">
-        <v>1850</v>
+        <v>1840</v>
       </c>
       <c r="N9">
         <v>90</v>
       </c>
       <c r="O9">
-        <v>1920</v>
+        <v>1910</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -2238,7 +2248,7 @@
         <v>730</v>
       </c>
       <c r="O28">
-        <v>6390</v>
+        <v>6400</v>
       </c>
       <c r="P28">
         <v>630</v>
@@ -2435,6 +2445,9 @@
       <c r="K3">
         <v>-7.41</v>
       </c>
+      <c r="L3">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
@@ -2520,6 +2533,9 @@
       <c r="K5">
         <v>-8.5</v>
       </c>
+      <c r="L5">
+        <v>1.47</v>
+      </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
@@ -2605,6 +2621,9 @@
       <c r="K7">
         <v>-3.06</v>
       </c>
+      <c r="L7">
+        <v>0.31</v>
+      </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
@@ -2690,6 +2709,9 @@
       <c r="K9">
         <v>-2.45</v>
       </c>
+      <c r="L9">
+        <v>-0.9399999999999999</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
@@ -2775,6 +2797,9 @@
       <c r="K11">
         <v>7.98</v>
       </c>
+      <c r="L11">
+        <v>12.46</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
@@ -2918,6 +2943,9 @@
       <c r="K15">
         <v>-8.42</v>
       </c>
+      <c r="L15">
+        <v>0.34</v>
+      </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
@@ -3052,6 +3080,9 @@
       <c r="K19">
         <v>-17.84</v>
       </c>
+      <c r="L19">
+        <v>-10.7</v>
+      </c>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
@@ -3201,6 +3232,9 @@
       <c r="K23">
         <v>-4.3</v>
       </c>
+      <c r="L23">
+        <v>-0.79</v>
+      </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
@@ -3268,6 +3302,9 @@
       <c r="K25">
         <v>-29.07</v>
       </c>
+      <c r="L25">
+        <v>-24.22</v>
+      </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
@@ -3399,6 +3436,9 @@
       <c r="K29">
         <v>-4.27</v>
       </c>
+      <c r="L29">
+        <v>-1.73</v>
+      </c>
     </row>
     <row r="30" spans="1:16">
       <c r="A30" t="s">
@@ -3484,6 +3524,9 @@
       <c r="K31">
         <v>-9.710000000000001</v>
       </c>
+      <c r="L31">
+        <v>-6.13</v>
+      </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" t="s">
@@ -3569,6 +3612,9 @@
       <c r="K33">
         <v>2.44</v>
       </c>
+      <c r="L33">
+        <v>6.07</v>
+      </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" t="s">
@@ -3815,6 +3861,9 @@
       <c r="K39">
         <v>-7.23</v>
       </c>
+      <c r="L39">
+        <v>-4.22</v>
+      </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" t="s">
@@ -3900,6 +3949,9 @@
       <c r="K41">
         <v>-1.78</v>
       </c>
+      <c r="L41">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" t="s">
@@ -3973,6 +4025,9 @@
       <c r="K43">
         <v>5.86</v>
       </c>
+      <c r="L43">
+        <v>9.59</v>
+      </c>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" t="s">
@@ -4058,6 +4113,9 @@
       <c r="K45">
         <v>-4.54</v>
       </c>
+      <c r="L45">
+        <v>-0.59</v>
+      </c>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" t="s">
@@ -4143,6 +4201,9 @@
       <c r="K47">
         <v>-5.65</v>
       </c>
+      <c r="L47">
+        <v>-3.38</v>
+      </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" t="s">
@@ -4228,6 +4289,9 @@
       <c r="K49">
         <v>-4.34</v>
       </c>
+      <c r="L49">
+        <v>0.5600000000000001</v>
+      </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" t="s">
@@ -4313,6 +4377,9 @@
       <c r="K51">
         <v>-4.09</v>
       </c>
+      <c r="L51">
+        <v>-0.52</v>
+      </c>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" t="s">
@@ -4458,6 +4525,9 @@
       </c>
       <c r="K55">
         <v>-7.38</v>
+      </c>
+      <c r="L55">
+        <v>-0.57</v>
       </c>
     </row>
   </sheetData>
@@ -4467,139 +4537,477 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1">
+    <row r="1" spans="1:5" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2">
-        <v>2024</v>
-      </c>
-      <c r="C2">
-        <v>2025</v>
-      </c>
-      <c r="D2" t="s">
-        <v>163</v>
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>4.69</v>
       </c>
       <c r="E2">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I2">
-        <v>27</v>
-      </c>
-      <c r="J2">
-        <v>1.013</v>
-      </c>
-      <c r="K2">
-        <v>1.3</v>
-      </c>
-      <c r="L2">
-        <v>0.4068579922006016</v>
-      </c>
-      <c r="M2">
-        <v>0.5</v>
-      </c>
-      <c r="N2">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3">
-        <v>2025</v>
-      </c>
-      <c r="C3">
-        <v>2026</v>
-      </c>
-      <c r="D3" t="s">
-        <v>166</v>
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>1.68</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I3">
-        <v>25</v>
-      </c>
-      <c r="J3">
-        <v>0.9985000000000001</v>
-      </c>
-      <c r="K3">
-        <v>-0.15</v>
-      </c>
-      <c r="L3">
-        <v>1.292640383940548</v>
-      </c>
-      <c r="M3">
-        <v>-2.68</v>
-      </c>
-      <c r="N3">
-        <v>2.38</v>
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5">
+        <v>1.13</v>
+      </c>
+      <c r="E5">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6">
+        <v>3.21</v>
+      </c>
+      <c r="E6">
+        <v>13.56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E7">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8">
+        <v>0.77</v>
+      </c>
+      <c r="E8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10">
+        <v>0.89</v>
+      </c>
+      <c r="E10">
+        <v>-2.64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11">
+        <v>0.13</v>
+      </c>
+      <c r="E11">
+        <v>6.83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12">
+        <v>-0.49</v>
+      </c>
+      <c r="E12">
+        <v>-5.14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13">
+        <v>2.67</v>
+      </c>
+      <c r="E13">
+        <v>-3.77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15">
+        <v>4.5</v>
+      </c>
+      <c r="E15">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16">
+        <v>-0.1</v>
+      </c>
+      <c r="E16">
+        <v>-9.390000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17">
+        <v>3.29</v>
+      </c>
+      <c r="E17">
+        <v>7.54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18">
+        <v>5.09</v>
+      </c>
+      <c r="E18">
+        <v>16.23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19">
+        <v>-1.06</v>
+      </c>
+      <c r="E19">
+        <v>-13.97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20">
+        <v>-0.85</v>
+      </c>
+      <c r="E20">
+        <v>-5.95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21">
+        <v>2.32</v>
+      </c>
+      <c r="E21">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22">
+        <v>-0.95</v>
+      </c>
+      <c r="E22">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23">
+        <v>0.89</v>
+      </c>
+      <c r="E23">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24">
+        <v>-0.45</v>
+      </c>
+      <c r="E24">
+        <v>-5.84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25">
+        <v>2.28</v>
+      </c>
+      <c r="E25">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26">
+        <v>0.49</v>
+      </c>
+      <c r="E26">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27">
+        <v>3.74</v>
+      </c>
+      <c r="E27">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28">
+        <v>3.92</v>
+      </c>
+      <c r="E28">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -4609,51 +5017,51 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -4667,37 +5075,37 @@
         <v>2025</v>
       </c>
       <c r="D2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H2" t="s">
         <v>167</v>
-      </c>
-      <c r="H2" t="s">
-        <v>165</v>
       </c>
       <c r="I2">
         <v>27</v>
       </c>
       <c r="J2">
-        <v>1.0134</v>
+        <v>1.013</v>
       </c>
       <c r="K2">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="L2">
-        <v>0.4204257713258387</v>
+        <v>0.4068579922006016</v>
       </c>
       <c r="M2">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="N2">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -4711,81 +5119,37 @@
         <v>2026</v>
       </c>
       <c r="D3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H3" t="s">
         <v>167</v>
-      </c>
-      <c r="H3" t="s">
-        <v>165</v>
       </c>
       <c r="I3">
         <v>25</v>
       </c>
       <c r="J3">
-        <v>0.9985000000000001</v>
+        <v>0.9962</v>
       </c>
       <c r="K3">
-        <v>-0.15</v>
+        <v>-0.38</v>
       </c>
       <c r="L3">
-        <v>1.292640383940548</v>
+        <v>1.274889510008675</v>
       </c>
       <c r="M3">
-        <v>-2.68</v>
+        <v>-2.88</v>
       </c>
       <c r="N3">
-        <v>2.38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4">
-        <v>2024</v>
-      </c>
-      <c r="C4">
-        <v>2026</v>
-      </c>
-      <c r="D4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H4" t="s">
-        <v>169</v>
-      </c>
-      <c r="I4">
-        <v>27</v>
-      </c>
-      <c r="J4">
-        <v>1.0119</v>
-      </c>
-      <c r="K4">
-        <v>1.19</v>
-      </c>
-      <c r="L4">
-        <v>1.37559344073835</v>
-      </c>
-      <c r="M4">
-        <v>-1.51</v>
-      </c>
-      <c r="N4">
-        <v>3.89</v>
+        <v>2.12</v>
       </c>
     </row>
   </sheetData>
@@ -4795,7 +5159,193 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <v>2024</v>
+      </c>
+      <c r="C2">
+        <v>2025</v>
+      </c>
+      <c r="D2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I2">
+        <v>27</v>
+      </c>
+      <c r="J2">
+        <v>1.0129</v>
+      </c>
+      <c r="K2">
+        <v>1.29</v>
+      </c>
+      <c r="L2">
+        <v>0.4198559945231114</v>
+      </c>
+      <c r="M2">
+        <v>0.47</v>
+      </c>
+      <c r="N2">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>2025</v>
+      </c>
+      <c r="C3">
+        <v>2026</v>
+      </c>
+      <c r="D3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I3">
+        <v>25</v>
+      </c>
+      <c r="J3">
+        <v>0.9962</v>
+      </c>
+      <c r="K3">
+        <v>-0.38</v>
+      </c>
+      <c r="L3">
+        <v>1.274889510008675</v>
+      </c>
+      <c r="M3">
+        <v>-2.88</v>
+      </c>
+      <c r="N3">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
+        <v>2024</v>
+      </c>
+      <c r="C4">
+        <v>2026</v>
+      </c>
+      <c r="D4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G4" t="s">
+        <v>169</v>
+      </c>
+      <c r="H4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I4">
+        <v>27</v>
+      </c>
+      <c r="J4">
+        <v>1.0091</v>
+      </c>
+      <c r="K4">
+        <v>0.91</v>
+      </c>
+      <c r="L4">
+        <v>1.357393872263498</v>
+      </c>
+      <c r="M4">
+        <v>-1.75</v>
+      </c>
+      <c r="N4">
+        <v>3.57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
@@ -4806,40 +5356,40 @@
         <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -4853,34 +5403,34 @@
         <v>45992</v>
       </c>
       <c r="D2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F2">
-        <v>1.0112</v>
+        <v>1.0114</v>
       </c>
       <c r="G2">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="H2">
         <v>0.2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K2">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="L2">
         <v>1.41</v>
       </c>
       <c r="M2">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4894,31 +5444,31 @@
         <v>46023</v>
       </c>
       <c r="D3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F3">
-        <v>1.0125</v>
+        <v>1.0127</v>
       </c>
       <c r="G3">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="H3">
         <v>0.1</v>
       </c>
       <c r="I3">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K3">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="L3">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="M3">
         <v>0.57</v>
@@ -4935,34 +5485,34 @@
         <v>46054</v>
       </c>
       <c r="D4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F4">
-        <v>1.0117</v>
+        <v>1.012</v>
       </c>
       <c r="G4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="H4">
         <v>-0.3</v>
       </c>
       <c r="I4">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K4">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="L4">
         <v>2.22</v>
       </c>
       <c r="M4">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4976,16 +5526,16 @@
         <v>46082</v>
       </c>
       <c r="D5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F5">
-        <v>1.0119</v>
+        <v>1.0123</v>
       </c>
       <c r="G5">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="H5">
         <v>-0.6</v>
@@ -4994,13 +5544,13 @@
         <v>3</v>
       </c>
       <c r="J5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K5">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L5">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="M5">
         <v>0.85</v>
@@ -5017,34 +5567,34 @@
         <v>46113</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F6">
-        <v>1.0018</v>
+        <v>1.0121</v>
       </c>
       <c r="G6">
-        <v>0.18</v>
+        <v>1.21</v>
       </c>
       <c r="H6">
-        <v>-2.8</v>
+        <v>-0.9</v>
       </c>
       <c r="I6">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K6">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L6">
-        <v>4.44</v>
+        <v>3.05</v>
       </c>
       <c r="M6">
-        <v>1.41</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -5058,34 +5608,34 @@
         <v>46143</v>
       </c>
       <c r="D7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F7">
-        <v>0.9982</v>
+        <v>1.0087</v>
       </c>
       <c r="G7">
-        <v>-0.18</v>
+        <v>0.87</v>
       </c>
       <c r="H7">
-        <v>-3.4</v>
+        <v>-1.5</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K7">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L7">
-        <v>4.79</v>
+        <v>3.53</v>
       </c>
       <c r="M7">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -5099,34 +5649,34 @@
         <v>46174</v>
       </c>
       <c r="D8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F8">
-        <v>1.0001</v>
+        <v>1.0106</v>
       </c>
       <c r="G8">
-        <v>0.01</v>
+        <v>1.06</v>
       </c>
       <c r="H8">
-        <v>-3.4</v>
+        <v>-1.6</v>
       </c>
       <c r="I8">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K8">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L8">
-        <v>5.14</v>
+        <v>3.97</v>
       </c>
       <c r="M8">
-        <v>1.63</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5140,34 +5690,75 @@
         <v>46204</v>
       </c>
       <c r="D9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F9">
-        <v>0.9964</v>
+        <v>1.007</v>
       </c>
       <c r="G9">
-        <v>-0.36</v>
+        <v>0.7</v>
       </c>
       <c r="H9">
-        <v>-3.9</v>
+        <v>-2.2</v>
       </c>
       <c r="I9">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K9">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L9">
-        <v>5.31</v>
+        <v>4.2</v>
       </c>
       <c r="M9">
-        <v>1.68</v>
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10">
+        <v>2026</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46235</v>
+      </c>
+      <c r="D10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F10">
+        <v>1.0067</v>
+      </c>
+      <c r="G10">
+        <v>0.67</v>
+      </c>
+      <c r="H10">
+        <v>-2.3</v>
+      </c>
+      <c r="I10">
+        <v>3.7</v>
+      </c>
+      <c r="J10">
+        <v>17</v>
+      </c>
+      <c r="K10">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L10">
+        <v>4.43</v>
+      </c>
+      <c r="M10">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>
